--- a/Backend/public/docs/proveedores-personas-format-hn.xlsx
+++ b/Backend/public/docs/proveedores-personas-format-hn.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="18">
   <si>
     <t>nombre</t>
   </si>
@@ -23,7 +23,10 @@
     <t>apellido</t>
   </si>
   <si>
-    <t>rtn</t>
+    <t>N. de Identificación</t>
+  </si>
+  <si>
+    <t>nit</t>
   </si>
   <si>
     <t>direccion</t>
@@ -47,7 +50,10 @@
     <t>Pérez</t>
   </si>
   <si>
-    <t>0801199900123</t>
+    <t>0801-1990-00123</t>
+  </si>
+  <si>
+    <t>08011990001234</t>
   </si>
   <si>
     <t>Col. Centro</t>
@@ -57,6 +63,9 @@
   </si>
   <si>
     <t>Francisco Morazán</t>
+  </si>
+  <si>
+    <t>99999999</t>
   </si>
   <si>
     <t>juan@ejemplo.com</t>
@@ -415,20 +424,21 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:I2"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="8.141" bestFit="true" customWidth="true" style="0"/>
     <col min="2" max="2" width="10.569" bestFit="true" customWidth="true" style="0"/>
-    <col min="3" max="3" width="16.425" bestFit="true" customWidth="true" style="0"/>
-    <col min="4" max="4" width="13.997" bestFit="true" customWidth="true" style="0"/>
-    <col min="5" max="5" width="19.995" bestFit="true" customWidth="true" style="0"/>
-    <col min="6" max="6" width="21.138" bestFit="true" customWidth="true" style="0"/>
-    <col min="7" max="7" width="10.569" bestFit="true" customWidth="true" style="0"/>
-    <col min="8" max="8" width="19.995" bestFit="true" customWidth="true" style="0"/>
+    <col min="3" max="3" width="24.708" bestFit="true" customWidth="true" style="0"/>
+    <col min="4" max="4" width="17.567" bestFit="true" customWidth="true" style="0"/>
+    <col min="5" max="5" width="13.997" bestFit="true" customWidth="true" style="0"/>
+    <col min="6" max="6" width="19.995" bestFit="true" customWidth="true" style="0"/>
+    <col min="7" max="7" width="21.138" bestFit="true" customWidth="true" style="0"/>
+    <col min="8" max="8" width="10.569" bestFit="true" customWidth="true" style="0"/>
+    <col min="9" max="9" width="19.995" bestFit="true" customWidth="true" style="0"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -453,31 +463,37 @@
       <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:9">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G2">
-        <v>99999999</v>
+        <v>14</v>
+      </c>
+      <c r="G2" t="s">
+        <v>15</v>
       </c>
       <c r="H2" t="s">
-        <v>14</v>
+        <v>16</v>
+      </c>
+      <c r="I2" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>

--- a/Backend/public/docs/proveedores-personas-format-hn.xlsx
+++ b/Backend/public/docs/proveedores-personas-format-hn.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="23">
   <si>
     <t>nombre</t>
   </si>
@@ -42,6 +42,21 @@
   </si>
   <si>
     <t>correo</t>
+  </si>
+  <si>
+    <t>Banco</t>
+  </si>
+  <si>
+    <t>Tipo_cuenta</t>
+  </si>
+  <si>
+    <t>Numero_cuenta</t>
+  </si>
+  <si>
+    <t>Titular_cuenta</t>
+  </si>
+  <si>
+    <t>Forma_pago</t>
   </si>
   <si>
     <t>Juan</t>
@@ -424,21 +439,21 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="8.141" bestFit="true" customWidth="true" style="0"/>
-    <col min="2" max="2" width="10.569" bestFit="true" customWidth="true" style="0"/>
-    <col min="3" max="3" width="24.708" bestFit="true" customWidth="true" style="0"/>
-    <col min="4" max="4" width="17.567" bestFit="true" customWidth="true" style="0"/>
-    <col min="5" max="5" width="13.997" bestFit="true" customWidth="true" style="0"/>
-    <col min="6" max="6" width="19.995" bestFit="true" customWidth="true" style="0"/>
-    <col min="7" max="7" width="21.138" bestFit="true" customWidth="true" style="0"/>
-    <col min="8" max="8" width="10.569" bestFit="true" customWidth="true" style="0"/>
-    <col min="9" max="9" width="19.995" bestFit="true" customWidth="true" style="0"/>
+    <col min="1" max="1" width="8.141" customWidth="true" style="0"/>
+    <col min="2" max="2" width="10.569" customWidth="true" style="0"/>
+    <col min="3" max="3" width="24.708" customWidth="true" style="0"/>
+    <col min="4" max="4" width="17.567" customWidth="true" style="0"/>
+    <col min="5" max="5" width="13.997" customWidth="true" style="0"/>
+    <col min="6" max="6" width="19.995" customWidth="true" style="0"/>
+    <col min="7" max="7" width="21.138" customWidth="true" style="0"/>
+    <col min="8" max="8" width="10.569" customWidth="true" style="0"/>
+    <col min="9" max="9" width="19.995" customWidth="true" style="0"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:14">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -466,34 +481,49 @@
       <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s">
+        <v>13</v>
+      </c>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="D2" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E2" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="F2" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="G2" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="H2" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>
